--- a/Data/eMobility/mG4sData/mg4sRevenue/hbtData.xlsx
+++ b/Data/eMobility/mG4sData/mg4sRevenue/hbtData.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Drivelectric\Fleet\MG4s\Revenue\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Operational Intelligence Hub\Data\eMobility\mG4sData\mg4sRevenue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429737C9-ABD4-495D-AC25-D8C58398D749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7FBDCB-D64C-4E95-A9A9-73A7F8F889F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$A$631</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="10">
   <si>
     <t>Date</t>
   </si>
@@ -55,12 +61,6 @@
   </si>
   <si>
     <t>KDT 136R</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>KD</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C631"/>
+  <dimension ref="A1:C1058"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" style="1" bestFit="1" customWidth="1"/>
@@ -7363,3744 +7363,4708 @@
         <v>4700</v>
       </c>
     </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A632" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B632" t="s">
+        <v>3</v>
+      </c>
+      <c r="C632" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A633" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B633" t="s">
+        <v>4</v>
+      </c>
+      <c r="C633" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A634" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B634" t="s">
+        <v>5</v>
+      </c>
+      <c r="C634" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A635" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B635" t="s">
+        <v>6</v>
+      </c>
+      <c r="C635" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A636" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B636" t="s">
+        <v>7</v>
+      </c>
+      <c r="C636" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A637" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B637" t="s">
+        <v>8</v>
+      </c>
+      <c r="C637" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A638" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B638" t="s">
+        <v>9</v>
+      </c>
+      <c r="C638" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A639" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B639" t="s">
+        <v>3</v>
+      </c>
+      <c r="C639" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A640" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B640" t="s">
+        <v>4</v>
+      </c>
+      <c r="C640" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A641" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B641" t="s">
+        <v>5</v>
+      </c>
+      <c r="C641" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A642" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B642" t="s">
+        <v>6</v>
+      </c>
+      <c r="C642" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A643" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B643" t="s">
+        <v>7</v>
+      </c>
+      <c r="C643" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A644" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B644" t="s">
+        <v>8</v>
+      </c>
+      <c r="C644" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A645" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B645" t="s">
+        <v>9</v>
+      </c>
+      <c r="C645" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A646" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B646" t="s">
+        <v>3</v>
+      </c>
+      <c r="C646" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A647" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B647" t="s">
+        <v>4</v>
+      </c>
+      <c r="C647" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A648" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B648" t="s">
+        <v>5</v>
+      </c>
+      <c r="C648" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A649" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B649" t="s">
+        <v>6</v>
+      </c>
+      <c r="C649" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A650" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B650" t="s">
+        <v>7</v>
+      </c>
+      <c r="C650" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A651" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B651" t="s">
+        <v>8</v>
+      </c>
+      <c r="C651" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A652" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B652" t="s">
+        <v>9</v>
+      </c>
+      <c r="C652" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A653" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B653" t="s">
+        <v>3</v>
+      </c>
+      <c r="C653" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A654" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B654" t="s">
+        <v>4</v>
+      </c>
+      <c r="C654" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A655" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B655" t="s">
+        <v>5</v>
+      </c>
+      <c r="C655" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A656" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B656" t="s">
+        <v>6</v>
+      </c>
+      <c r="C656" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A657" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B657" t="s">
+        <v>7</v>
+      </c>
+      <c r="C657" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A658" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B658" t="s">
+        <v>8</v>
+      </c>
+      <c r="C658" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A659" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B659" t="s">
+        <v>9</v>
+      </c>
+      <c r="C659" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A660" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B660" t="s">
+        <v>3</v>
+      </c>
+      <c r="C660" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A661" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B661" t="s">
+        <v>4</v>
+      </c>
+      <c r="C661" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A662" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B662" t="s">
+        <v>5</v>
+      </c>
+      <c r="C662" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A663" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B663" t="s">
+        <v>6</v>
+      </c>
+      <c r="C663" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A664" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B664" t="s">
+        <v>7</v>
+      </c>
+      <c r="C664" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A665" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B665" t="s">
+        <v>8</v>
+      </c>
+      <c r="C665" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A666" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B666" t="s">
+        <v>9</v>
+      </c>
+      <c r="C666" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A667" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B667" t="s">
+        <v>3</v>
+      </c>
+      <c r="C667" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A668" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B668" t="s">
+        <v>4</v>
+      </c>
+      <c r="C668" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A669" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B669" t="s">
+        <v>5</v>
+      </c>
+      <c r="C669" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A670" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B670" t="s">
+        <v>6</v>
+      </c>
+      <c r="C670" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A671" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B671" t="s">
+        <v>7</v>
+      </c>
+      <c r="C671" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A672" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B672" t="s">
+        <v>8</v>
+      </c>
+      <c r="C672" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A673" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B673" t="s">
+        <v>9</v>
+      </c>
+      <c r="C673" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A674" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B674" t="s">
+        <v>3</v>
+      </c>
+      <c r="C674" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A675" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B675" t="s">
+        <v>4</v>
+      </c>
+      <c r="C675" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A676" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B676" t="s">
+        <v>5</v>
+      </c>
+      <c r="C676" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A677" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B677" t="s">
+        <v>6</v>
+      </c>
+      <c r="C677" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A678" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B678" t="s">
+        <v>7</v>
+      </c>
+      <c r="C678" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A679" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B679" t="s">
+        <v>8</v>
+      </c>
+      <c r="C679" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A680" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B680" t="s">
+        <v>9</v>
+      </c>
+      <c r="C680" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A681" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B681" t="s">
+        <v>3</v>
+      </c>
+      <c r="C681" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A682" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B682" t="s">
+        <v>4</v>
+      </c>
+      <c r="C682" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A683" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B683" t="s">
+        <v>5</v>
+      </c>
+      <c r="C683" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A684" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B684" t="s">
+        <v>6</v>
+      </c>
+      <c r="C684" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A685" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B685" t="s">
+        <v>7</v>
+      </c>
+      <c r="C685" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A686" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B686" t="s">
+        <v>8</v>
+      </c>
+      <c r="C686" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A687" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B687" t="s">
+        <v>9</v>
+      </c>
+      <c r="C687" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A688" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B688" t="s">
+        <v>3</v>
+      </c>
+      <c r="C688" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A689" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B689" t="s">
+        <v>4</v>
+      </c>
+      <c r="C689" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A690" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B690" t="s">
+        <v>5</v>
+      </c>
+      <c r="C690" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A691" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B691" t="s">
+        <v>6</v>
+      </c>
+      <c r="C691" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A692" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B692" t="s">
+        <v>7</v>
+      </c>
+      <c r="C692" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A693" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B693" t="s">
+        <v>8</v>
+      </c>
+      <c r="C693" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A694" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B694" t="s">
+        <v>9</v>
+      </c>
+      <c r="C694" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A695" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B695" t="s">
+        <v>3</v>
+      </c>
+      <c r="C695" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A696" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B696" t="s">
+        <v>4</v>
+      </c>
+      <c r="C696" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A697" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B697" t="s">
+        <v>5</v>
+      </c>
+      <c r="C697" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A698" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B698" t="s">
+        <v>6</v>
+      </c>
+      <c r="C698" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A699" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B699" t="s">
+        <v>7</v>
+      </c>
+      <c r="C699" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A700" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B700" t="s">
+        <v>8</v>
+      </c>
+      <c r="C700" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A701" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B701" t="s">
+        <v>9</v>
+      </c>
+      <c r="C701" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A702" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B702" t="s">
+        <v>3</v>
+      </c>
+      <c r="C702" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A703" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B703" t="s">
+        <v>4</v>
+      </c>
+      <c r="C703" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A704" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B704" t="s">
+        <v>5</v>
+      </c>
+      <c r="C704" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A705" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B705" t="s">
+        <v>6</v>
+      </c>
+      <c r="C705" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A706" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B706" t="s">
+        <v>7</v>
+      </c>
+      <c r="C706" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A707" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B707" t="s">
+        <v>8</v>
+      </c>
+      <c r="C707" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A708" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B708" t="s">
+        <v>9</v>
+      </c>
+      <c r="C708" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A709" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B709" t="s">
+        <v>3</v>
+      </c>
+      <c r="C709" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A710" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B710" t="s">
+        <v>4</v>
+      </c>
+      <c r="C710" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A711" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B711" t="s">
+        <v>5</v>
+      </c>
+      <c r="C711" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A712" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B712" t="s">
+        <v>6</v>
+      </c>
+      <c r="C712" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A713" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B713" t="s">
+        <v>7</v>
+      </c>
+      <c r="C713" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A714" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B714" t="s">
+        <v>8</v>
+      </c>
+      <c r="C714" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A715" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B715" t="s">
+        <v>9</v>
+      </c>
+      <c r="C715" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A716" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B716" t="s">
+        <v>3</v>
+      </c>
+      <c r="C716" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A717" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B717" t="s">
+        <v>4</v>
+      </c>
+      <c r="C717" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A718" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B718" t="s">
+        <v>5</v>
+      </c>
+      <c r="C718" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A719" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B719" t="s">
+        <v>6</v>
+      </c>
+      <c r="C719" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A720" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B720" t="s">
+        <v>7</v>
+      </c>
+      <c r="C720" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A721" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B721" t="s">
+        <v>8</v>
+      </c>
+      <c r="C721" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A722" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B722" t="s">
+        <v>9</v>
+      </c>
+      <c r="C722" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A723" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B723" t="s">
+        <v>3</v>
+      </c>
+      <c r="C723" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A724" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B724" t="s">
+        <v>4</v>
+      </c>
+      <c r="C724" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A725" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B725" t="s">
+        <v>5</v>
+      </c>
+      <c r="C725" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A726" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B726" t="s">
+        <v>6</v>
+      </c>
+      <c r="C726" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A727" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B727" t="s">
+        <v>7</v>
+      </c>
+      <c r="C727" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A728" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B728" t="s">
+        <v>8</v>
+      </c>
+      <c r="C728" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A729" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B729" t="s">
+        <v>9</v>
+      </c>
+      <c r="C729" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A730" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B730" t="s">
+        <v>3</v>
+      </c>
+      <c r="C730" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A731" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B731" t="s">
+        <v>4</v>
+      </c>
+      <c r="C731" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A732" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B732" t="s">
+        <v>5</v>
+      </c>
+      <c r="C732" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A733" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B733" t="s">
+        <v>6</v>
+      </c>
+      <c r="C733" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A734" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B734" t="s">
+        <v>7</v>
+      </c>
+      <c r="C734" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A735" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B735" t="s">
+        <v>8</v>
+      </c>
+      <c r="C735" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A736" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B736" t="s">
+        <v>9</v>
+      </c>
+      <c r="C736" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A737" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B737" t="s">
+        <v>3</v>
+      </c>
+      <c r="C737" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A738" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B738" t="s">
+        <v>4</v>
+      </c>
+      <c r="C738" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A739" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B739" t="s">
+        <v>5</v>
+      </c>
+      <c r="C739" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A740" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B740" t="s">
+        <v>6</v>
+      </c>
+      <c r="C740" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A741" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B741" t="s">
+        <v>7</v>
+      </c>
+      <c r="C741" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A742" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B742" t="s">
+        <v>8</v>
+      </c>
+      <c r="C742" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A743" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B743" t="s">
+        <v>9</v>
+      </c>
+      <c r="C743" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A744" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B744" t="s">
+        <v>3</v>
+      </c>
+      <c r="C744" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A745" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B745" t="s">
+        <v>4</v>
+      </c>
+      <c r="C745" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A746" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B746" t="s">
+        <v>5</v>
+      </c>
+      <c r="C746" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A747" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B747" t="s">
+        <v>6</v>
+      </c>
+      <c r="C747" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A748" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B748" t="s">
+        <v>7</v>
+      </c>
+      <c r="C748" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A749" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B749" t="s">
+        <v>8</v>
+      </c>
+      <c r="C749" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A750" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B750" t="s">
+        <v>9</v>
+      </c>
+      <c r="C750" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A751" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B751" t="s">
+        <v>3</v>
+      </c>
+      <c r="C751" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A752" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B752" t="s">
+        <v>4</v>
+      </c>
+      <c r="C752" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A753" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B753" t="s">
+        <v>5</v>
+      </c>
+      <c r="C753" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A754" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B754" t="s">
+        <v>6</v>
+      </c>
+      <c r="C754" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A755" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B755" t="s">
+        <v>7</v>
+      </c>
+      <c r="C755" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A756" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B756" t="s">
+        <v>8</v>
+      </c>
+      <c r="C756" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A757" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B757" t="s">
+        <v>9</v>
+      </c>
+      <c r="C757" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A758" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B758" t="s">
+        <v>3</v>
+      </c>
+      <c r="C758" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A759" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B759" t="s">
+        <v>4</v>
+      </c>
+      <c r="C759" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A760" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B760" t="s">
+        <v>5</v>
+      </c>
+      <c r="C760" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A761" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B761" t="s">
+        <v>6</v>
+      </c>
+      <c r="C761" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A762" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B762" t="s">
+        <v>7</v>
+      </c>
+      <c r="C762" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A763" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B763" t="s">
+        <v>8</v>
+      </c>
+      <c r="C763" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A764" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B764" t="s">
+        <v>9</v>
+      </c>
+      <c r="C764" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A765" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B765" t="s">
+        <v>3</v>
+      </c>
+      <c r="C765" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A766" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B766" t="s">
+        <v>4</v>
+      </c>
+      <c r="C766" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A767" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B767" t="s">
+        <v>5</v>
+      </c>
+      <c r="C767" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A768" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B768" t="s">
+        <v>6</v>
+      </c>
+      <c r="C768" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A769" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B769" t="s">
+        <v>7</v>
+      </c>
+      <c r="C769" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A770" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B770" t="s">
+        <v>8</v>
+      </c>
+      <c r="C770" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A771" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B771" t="s">
+        <v>9</v>
+      </c>
+      <c r="C771" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A772" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B772" t="s">
+        <v>3</v>
+      </c>
+      <c r="C772" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A773" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B773" t="s">
+        <v>4</v>
+      </c>
+      <c r="C773" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A774" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B774" t="s">
+        <v>5</v>
+      </c>
+      <c r="C774" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A775" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B775" t="s">
+        <v>6</v>
+      </c>
+      <c r="C775" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A776" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B776" t="s">
+        <v>7</v>
+      </c>
+      <c r="C776" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A777" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B777" t="s">
+        <v>8</v>
+      </c>
+      <c r="C777" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A778" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B778" t="s">
+        <v>9</v>
+      </c>
+      <c r="C778" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A779" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B779" t="s">
+        <v>3</v>
+      </c>
+      <c r="C779" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A780" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B780" t="s">
+        <v>4</v>
+      </c>
+      <c r="C780" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A781" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B781" t="s">
+        <v>5</v>
+      </c>
+      <c r="C781" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A782" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B782" t="s">
+        <v>6</v>
+      </c>
+      <c r="C782" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A783" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B783" t="s">
+        <v>7</v>
+      </c>
+      <c r="C783" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A784" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B784" t="s">
+        <v>8</v>
+      </c>
+      <c r="C784" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A785" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B785" t="s">
+        <v>9</v>
+      </c>
+      <c r="C785" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A786" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B786" t="s">
+        <v>3</v>
+      </c>
+      <c r="C786" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A787" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B787" t="s">
+        <v>4</v>
+      </c>
+      <c r="C787" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A788" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B788" t="s">
+        <v>5</v>
+      </c>
+      <c r="C788" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A789" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B789" t="s">
+        <v>6</v>
+      </c>
+      <c r="C789" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A790" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B790" t="s">
+        <v>7</v>
+      </c>
+      <c r="C790" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A791" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B791" t="s">
+        <v>8</v>
+      </c>
+      <c r="C791" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A792" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B792" t="s">
+        <v>9</v>
+      </c>
+      <c r="C792" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A793" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B793" t="s">
+        <v>3</v>
+      </c>
+      <c r="C793" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A794" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B794" t="s">
+        <v>4</v>
+      </c>
+      <c r="C794" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A795" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B795" t="s">
+        <v>5</v>
+      </c>
+      <c r="C795" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A796" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B796" t="s">
+        <v>6</v>
+      </c>
+      <c r="C796" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A797" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B797" t="s">
+        <v>7</v>
+      </c>
+      <c r="C797" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A798" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B798" t="s">
+        <v>8</v>
+      </c>
+      <c r="C798" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A799" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B799" t="s">
+        <v>9</v>
+      </c>
+      <c r="C799" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A800" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B800" t="s">
+        <v>3</v>
+      </c>
+      <c r="C800" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A801" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B801" t="s">
+        <v>4</v>
+      </c>
+      <c r="C801" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A802" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B802" t="s">
+        <v>5</v>
+      </c>
+      <c r="C802" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A803" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B803" t="s">
+        <v>6</v>
+      </c>
+      <c r="C803" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A804" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B804" t="s">
+        <v>7</v>
+      </c>
+      <c r="C804" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A805" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B805" t="s">
+        <v>8</v>
+      </c>
+      <c r="C805" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A806" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B806" t="s">
+        <v>9</v>
+      </c>
+      <c r="C806" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A807" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B807" t="s">
+        <v>3</v>
+      </c>
+      <c r="C807" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A808" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B808" t="s">
+        <v>4</v>
+      </c>
+      <c r="C808" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A809" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B809" t="s">
+        <v>5</v>
+      </c>
+      <c r="C809" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A810" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B810" t="s">
+        <v>6</v>
+      </c>
+      <c r="C810" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A811" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B811" t="s">
+        <v>7</v>
+      </c>
+      <c r="C811" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A812" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B812" t="s">
+        <v>8</v>
+      </c>
+      <c r="C812" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A813" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B813" t="s">
+        <v>9</v>
+      </c>
+      <c r="C813" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A814" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B814" t="s">
+        <v>3</v>
+      </c>
+      <c r="C814" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A815" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B815" t="s">
+        <v>4</v>
+      </c>
+      <c r="C815" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A816" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B816" t="s">
+        <v>5</v>
+      </c>
+      <c r="C816" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A817" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B817" t="s">
+        <v>6</v>
+      </c>
+      <c r="C817" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A818" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B818" t="s">
+        <v>7</v>
+      </c>
+      <c r="C818" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A819" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B819" t="s">
+        <v>8</v>
+      </c>
+      <c r="C819" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A820" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B820" t="s">
+        <v>9</v>
+      </c>
+      <c r="C820" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A821" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B821" t="s">
+        <v>3</v>
+      </c>
+      <c r="C821" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A822" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B822" t="s">
+        <v>4</v>
+      </c>
+      <c r="C822" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A823" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B823" t="s">
+        <v>5</v>
+      </c>
+      <c r="C823" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A824" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B824" t="s">
+        <v>6</v>
+      </c>
+      <c r="C824" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A825" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B825" t="s">
+        <v>7</v>
+      </c>
+      <c r="C825" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A826" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B826" t="s">
+        <v>8</v>
+      </c>
+      <c r="C826" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A827" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B827" t="s">
+        <v>9</v>
+      </c>
+      <c r="C827" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A828" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B828" t="s">
+        <v>3</v>
+      </c>
+      <c r="C828" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A829" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B829" t="s">
+        <v>4</v>
+      </c>
+      <c r="C829" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A830" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B830" t="s">
+        <v>5</v>
+      </c>
+      <c r="C830" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A831" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B831" t="s">
+        <v>6</v>
+      </c>
+      <c r="C831" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A832" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B832" t="s">
+        <v>7</v>
+      </c>
+      <c r="C832" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A833" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B833" t="s">
+        <v>8</v>
+      </c>
+      <c r="C833" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A834" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B834" t="s">
+        <v>9</v>
+      </c>
+      <c r="C834" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A835" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B835" t="s">
+        <v>3</v>
+      </c>
+      <c r="C835" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A836" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B836" t="s">
+        <v>4</v>
+      </c>
+      <c r="C836" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A837" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B837" t="s">
+        <v>5</v>
+      </c>
+      <c r="C837" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A838" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B838" t="s">
+        <v>6</v>
+      </c>
+      <c r="C838" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A839" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B839" t="s">
+        <v>7</v>
+      </c>
+      <c r="C839" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A840" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B840" t="s">
+        <v>8</v>
+      </c>
+      <c r="C840" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A841" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B841" t="s">
+        <v>9</v>
+      </c>
+      <c r="C841" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A842" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B842" t="s">
+        <v>3</v>
+      </c>
+      <c r="C842" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A843" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B843" t="s">
+        <v>4</v>
+      </c>
+      <c r="C843" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A844" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B844" t="s">
+        <v>5</v>
+      </c>
+      <c r="C844" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A845" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B845" t="s">
+        <v>6</v>
+      </c>
+      <c r="C845" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A846" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B846" t="s">
+        <v>7</v>
+      </c>
+      <c r="C846" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A847" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B847" t="s">
+        <v>8</v>
+      </c>
+      <c r="C847" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A848" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B848" t="s">
+        <v>9</v>
+      </c>
+      <c r="C848" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A849" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B849" t="s">
+        <v>3</v>
+      </c>
+      <c r="C849" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A850" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B850" t="s">
+        <v>4</v>
+      </c>
+      <c r="C850" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A851" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B851" t="s">
+        <v>5</v>
+      </c>
+      <c r="C851" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A852" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B852" t="s">
+        <v>6</v>
+      </c>
+      <c r="C852" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A853" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B853" t="s">
+        <v>7</v>
+      </c>
+      <c r="C853" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A854" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B854" t="s">
+        <v>8</v>
+      </c>
+      <c r="C854" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A855" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B855" t="s">
+        <v>9</v>
+      </c>
+      <c r="C855" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A856" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B856" t="s">
+        <v>3</v>
+      </c>
+      <c r="C856" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A857" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B857" t="s">
+        <v>4</v>
+      </c>
+      <c r="C857" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A858" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B858" t="s">
+        <v>5</v>
+      </c>
+      <c r="C858" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A859" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B859" t="s">
+        <v>6</v>
+      </c>
+      <c r="C859" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A860" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B860" t="s">
+        <v>7</v>
+      </c>
+      <c r="C860" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A861" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B861" t="s">
+        <v>8</v>
+      </c>
+      <c r="C861" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A862" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B862" t="s">
+        <v>9</v>
+      </c>
+      <c r="C862" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A863" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B863" t="s">
+        <v>3</v>
+      </c>
+      <c r="C863" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A864" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B864" t="s">
+        <v>4</v>
+      </c>
+      <c r="C864" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A865" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B865" t="s">
+        <v>5</v>
+      </c>
+      <c r="C865" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A866" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B866" t="s">
+        <v>6</v>
+      </c>
+      <c r="C866" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A867" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B867" t="s">
+        <v>7</v>
+      </c>
+      <c r="C867" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A868" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B868" t="s">
+        <v>8</v>
+      </c>
+      <c r="C868" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A869" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B869" t="s">
+        <v>9</v>
+      </c>
+      <c r="C869" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A870" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B870" t="s">
+        <v>3</v>
+      </c>
+      <c r="C870" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A871" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B871" t="s">
+        <v>4</v>
+      </c>
+      <c r="C871" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A872" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B872" t="s">
+        <v>5</v>
+      </c>
+      <c r="C872" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A873" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B873" t="s">
+        <v>6</v>
+      </c>
+      <c r="C873" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A874" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B874" t="s">
+        <v>7</v>
+      </c>
+      <c r="C874" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A875" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B875" t="s">
+        <v>8</v>
+      </c>
+      <c r="C875" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A876" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B876" t="s">
+        <v>9</v>
+      </c>
+      <c r="C876" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A877" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B877" t="s">
+        <v>3</v>
+      </c>
+      <c r="C877" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A878" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B878" t="s">
+        <v>4</v>
+      </c>
+      <c r="C878" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A879" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B879" t="s">
+        <v>5</v>
+      </c>
+      <c r="C879" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A880" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B880" t="s">
+        <v>6</v>
+      </c>
+      <c r="C880" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A881" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B881" t="s">
+        <v>7</v>
+      </c>
+      <c r="C881" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A882" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B882" t="s">
+        <v>8</v>
+      </c>
+      <c r="C882" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A883" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B883" t="s">
+        <v>9</v>
+      </c>
+      <c r="C883" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A884" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B884" t="s">
+        <v>3</v>
+      </c>
+      <c r="C884" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A885" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B885" t="s">
+        <v>4</v>
+      </c>
+      <c r="C885" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A886" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B886" t="s">
+        <v>5</v>
+      </c>
+      <c r="C886" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A887" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B887" t="s">
+        <v>6</v>
+      </c>
+      <c r="C887" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A888" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B888" t="s">
+        <v>7</v>
+      </c>
+      <c r="C888" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A889" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B889" t="s">
+        <v>8</v>
+      </c>
+      <c r="C889" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A890" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B890" t="s">
+        <v>9</v>
+      </c>
+      <c r="C890" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A891" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B891" t="s">
+        <v>3</v>
+      </c>
+      <c r="C891" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A892" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B892" t="s">
+        <v>4</v>
+      </c>
+      <c r="C892" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A893" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B893" t="s">
+        <v>5</v>
+      </c>
+      <c r="C893" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A894" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B894" t="s">
+        <v>6</v>
+      </c>
+      <c r="C894" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A895" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B895" t="s">
+        <v>7</v>
+      </c>
+      <c r="C895" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A896" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B896" t="s">
+        <v>8</v>
+      </c>
+      <c r="C896" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A897" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B897" t="s">
+        <v>9</v>
+      </c>
+      <c r="C897" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A898" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B898" t="s">
+        <v>3</v>
+      </c>
+      <c r="C898" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A899" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B899" t="s">
+        <v>4</v>
+      </c>
+      <c r="C899" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A900" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B900" t="s">
+        <v>5</v>
+      </c>
+      <c r="C900" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A901" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B901" t="s">
+        <v>6</v>
+      </c>
+      <c r="C901" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A902" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B902" t="s">
+        <v>7</v>
+      </c>
+      <c r="C902" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A903" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B903" t="s">
+        <v>8</v>
+      </c>
+      <c r="C903" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A904" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B904" t="s">
+        <v>9</v>
+      </c>
+      <c r="C904" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A905" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B905" t="s">
+        <v>3</v>
+      </c>
+      <c r="C905" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A906" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B906" t="s">
+        <v>4</v>
+      </c>
+      <c r="C906" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A907" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B907" t="s">
+        <v>5</v>
+      </c>
+      <c r="C907" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A908" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B908" t="s">
+        <v>6</v>
+      </c>
+      <c r="C908" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A909" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B909" t="s">
+        <v>7</v>
+      </c>
+      <c r="C909" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A910" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B910" t="s">
+        <v>8</v>
+      </c>
+      <c r="C910" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A911" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B911" t="s">
+        <v>9</v>
+      </c>
+      <c r="C911" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A912" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B912" t="s">
+        <v>3</v>
+      </c>
+      <c r="C912" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A913" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B913" t="s">
+        <v>4</v>
+      </c>
+      <c r="C913" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A914" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B914" t="s">
+        <v>5</v>
+      </c>
+      <c r="C914" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A915" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B915" t="s">
+        <v>6</v>
+      </c>
+      <c r="C915" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A916" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B916" t="s">
+        <v>7</v>
+      </c>
+      <c r="C916" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A917" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B917" t="s">
+        <v>8</v>
+      </c>
+      <c r="C917" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A918" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B918" t="s">
+        <v>9</v>
+      </c>
+      <c r="C918" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A919" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B919" t="s">
+        <v>3</v>
+      </c>
+      <c r="C919" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A920" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B920" t="s">
+        <v>4</v>
+      </c>
+      <c r="C920" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A921" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B921" t="s">
+        <v>5</v>
+      </c>
+      <c r="C921" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A922" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B922" t="s">
+        <v>6</v>
+      </c>
+      <c r="C922" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A923" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B923" t="s">
+        <v>7</v>
+      </c>
+      <c r="C923" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A924" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B924" t="s">
+        <v>8</v>
+      </c>
+      <c r="C924" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A925" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B925" t="s">
+        <v>9</v>
+      </c>
+      <c r="C925" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A926" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B926" t="s">
+        <v>3</v>
+      </c>
+      <c r="C926" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A927" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B927" t="s">
+        <v>4</v>
+      </c>
+      <c r="C927" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A928" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B928" t="s">
+        <v>5</v>
+      </c>
+      <c r="C928" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A929" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B929" t="s">
+        <v>6</v>
+      </c>
+      <c r="C929" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A930" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B930" t="s">
+        <v>7</v>
+      </c>
+      <c r="C930" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A931" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B931" t="s">
+        <v>8</v>
+      </c>
+      <c r="C931" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A932" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B932" t="s">
+        <v>9</v>
+      </c>
+      <c r="C932" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A933" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B933" t="s">
+        <v>3</v>
+      </c>
+      <c r="C933" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A934" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B934" t="s">
+        <v>4</v>
+      </c>
+      <c r="C934" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A935" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B935" t="s">
+        <v>5</v>
+      </c>
+      <c r="C935" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A936" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B936" t="s">
+        <v>6</v>
+      </c>
+      <c r="C936" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A937" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B937" t="s">
+        <v>7</v>
+      </c>
+      <c r="C937" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A938" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B938" t="s">
+        <v>8</v>
+      </c>
+      <c r="C938" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A939" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B939" t="s">
+        <v>9</v>
+      </c>
+      <c r="C939" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A940" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B940" t="s">
+        <v>3</v>
+      </c>
+      <c r="C940" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A941" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B941" t="s">
+        <v>4</v>
+      </c>
+      <c r="C941" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A942" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B942" t="s">
+        <v>5</v>
+      </c>
+      <c r="C942" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A943" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B943" t="s">
+        <v>6</v>
+      </c>
+      <c r="C943" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A944" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B944" t="s">
+        <v>7</v>
+      </c>
+      <c r="C944" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A945" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B945" t="s">
+        <v>8</v>
+      </c>
+      <c r="C945" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A946" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B946" t="s">
+        <v>9</v>
+      </c>
+      <c r="C946" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A947" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B947" t="s">
+        <v>3</v>
+      </c>
+      <c r="C947" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A948" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B948" t="s">
+        <v>4</v>
+      </c>
+      <c r="C948" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A949" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B949" t="s">
+        <v>5</v>
+      </c>
+      <c r="C949" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A950" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B950" t="s">
+        <v>6</v>
+      </c>
+      <c r="C950" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A951" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B951" t="s">
+        <v>7</v>
+      </c>
+      <c r="C951" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A952" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B952" t="s">
+        <v>8</v>
+      </c>
+      <c r="C952" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A953" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B953" t="s">
+        <v>9</v>
+      </c>
+      <c r="C953" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A954" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B954" t="s">
+        <v>3</v>
+      </c>
+      <c r="C954" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A955" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B955" t="s">
+        <v>4</v>
+      </c>
+      <c r="C955" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A956" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B956" t="s">
+        <v>5</v>
+      </c>
+      <c r="C956" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A957" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B957" t="s">
+        <v>6</v>
+      </c>
+      <c r="C957" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A958" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B958" t="s">
+        <v>7</v>
+      </c>
+      <c r="C958" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A959" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B959" t="s">
+        <v>8</v>
+      </c>
+      <c r="C959" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A960" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B960" t="s">
+        <v>9</v>
+      </c>
+      <c r="C960" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A961" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B961" t="s">
+        <v>3</v>
+      </c>
+      <c r="C961" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A962" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B962" t="s">
+        <v>4</v>
+      </c>
+      <c r="C962" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A963" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B963" t="s">
+        <v>5</v>
+      </c>
+      <c r="C963" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A964" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B964" t="s">
+        <v>6</v>
+      </c>
+      <c r="C964" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A965" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B965" t="s">
+        <v>7</v>
+      </c>
+      <c r="C965" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A966" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B966" t="s">
+        <v>8</v>
+      </c>
+      <c r="C966" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A967" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B967" t="s">
+        <v>9</v>
+      </c>
+      <c r="C967" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A968" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B968" t="s">
+        <v>3</v>
+      </c>
+      <c r="C968" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A969" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B969" t="s">
+        <v>4</v>
+      </c>
+      <c r="C969" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A970" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B970" t="s">
+        <v>5</v>
+      </c>
+      <c r="C970" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A971" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B971" t="s">
+        <v>6</v>
+      </c>
+      <c r="C971" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A972" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B972" t="s">
+        <v>7</v>
+      </c>
+      <c r="C972" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A973" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B973" t="s">
+        <v>8</v>
+      </c>
+      <c r="C973" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A974" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B974" t="s">
+        <v>9</v>
+      </c>
+      <c r="C974" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A975" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B975" t="s">
+        <v>3</v>
+      </c>
+      <c r="C975" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A976" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B976" t="s">
+        <v>4</v>
+      </c>
+      <c r="C976" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A977" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B977" t="s">
+        <v>5</v>
+      </c>
+      <c r="C977" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A978" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B978" t="s">
+        <v>6</v>
+      </c>
+      <c r="C978" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A979" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B979" t="s">
+        <v>7</v>
+      </c>
+      <c r="C979" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A980" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B980" t="s">
+        <v>8</v>
+      </c>
+      <c r="C980" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A981" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B981" t="s">
+        <v>9</v>
+      </c>
+      <c r="C981" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A982" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3</v>
+      </c>
+      <c r="C982" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A983" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B983" t="s">
+        <v>4</v>
+      </c>
+      <c r="C983" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A984" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B984" t="s">
+        <v>5</v>
+      </c>
+      <c r="C984" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A985" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B985" t="s">
+        <v>6</v>
+      </c>
+      <c r="C985" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A986" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B986" t="s">
+        <v>7</v>
+      </c>
+      <c r="C986" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A987" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B987" t="s">
+        <v>8</v>
+      </c>
+      <c r="C987" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A988" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B988" t="s">
+        <v>9</v>
+      </c>
+      <c r="C988" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A989" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B989" t="s">
+        <v>3</v>
+      </c>
+      <c r="C989" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A990" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B990" t="s">
+        <v>4</v>
+      </c>
+      <c r="C990" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A991" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B991" t="s">
+        <v>5</v>
+      </c>
+      <c r="C991" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A992" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B992" t="s">
+        <v>6</v>
+      </c>
+      <c r="C992" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A993" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B993" t="s">
+        <v>7</v>
+      </c>
+      <c r="C993" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A994" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B994" t="s">
+        <v>8</v>
+      </c>
+      <c r="C994" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A995" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B995" t="s">
+        <v>9</v>
+      </c>
+      <c r="C995" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A996" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B996" t="s">
+        <v>3</v>
+      </c>
+      <c r="C996" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A997" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B997" t="s">
+        <v>4</v>
+      </c>
+      <c r="C997" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A998" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B998" t="s">
+        <v>5</v>
+      </c>
+      <c r="C998" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A999" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B999" t="s">
+        <v>6</v>
+      </c>
+      <c r="C999" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1000" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1000" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1001" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1001" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1002" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1002" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1003" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1003" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1004" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1004" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1005" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1005" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1006" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1006" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1007" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1007" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1008" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1008" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1009" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1009" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1010" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1010" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1011" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1011" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1012" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1012" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1013" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1013" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1014" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1014" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1015" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1015" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1016" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1016" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1017" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1017" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1018" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1018" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1019" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1019" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1020" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1020" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1021" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1021" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1022" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1022" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1023" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1023" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1024" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1024" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1025" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1025" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1026" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1026" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1027" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1027" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1028" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1028" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1029" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1029" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1030" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1030" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1031" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1031" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1032" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1032" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1033" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1033" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1034" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1034" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1035" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1035" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1036" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1036" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1037" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1037" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1038" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1038" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1039" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1039" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1040" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1040" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1041" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1041" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1042" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1042" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1043" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1043" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1044" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1044" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1045" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1045" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1046" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1046" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1047" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1047" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1048" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1048" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1049" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1049" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1050" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1050" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1051" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1051" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1052" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1052" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1053" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1053" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1054" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1054" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1055" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1055" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1056" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1056" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1057" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1057" s="2">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1058" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1058" s="2">
+        <v>4700</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C631">
     <sortCondition ref="A1:A631"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810DBB15-66F7-4FDC-B41A-E2B67BC77525}">
-  <dimension ref="A1:A631"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>46029</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>46030</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="1">
-        <v>46032</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="1">
-        <v>46033</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="1">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" s="1">
-        <v>46035</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" s="1">
-        <v>46036</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A104" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A105" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" s="1">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A116" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" s="1">
-        <v>46039</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A126" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" s="1">
-        <v>46040</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A133" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" s="1">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A136" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" s="1">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A144" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A146" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A147" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A148" s="1">
-        <v>46043</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A149" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A150" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A151" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A152" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A153" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A154" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A155" s="1">
-        <v>46044</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A156" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A157" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A158" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A159" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A160" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A161" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A162" s="1">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A163" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A164" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A165" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A166" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A167" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A168" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A169" s="1">
-        <v>46046</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A170" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A171" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A172" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A173" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A174" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A175" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A176" s="1">
-        <v>46047</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A177" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A178" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A179" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A180" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A181" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A182" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A183" s="1">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A184" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A185" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A186" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A187" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A188" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A189" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A190" s="1">
-        <v>46049</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A191" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A192" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A193" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A194" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A195" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A196" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A197" s="1">
-        <v>46050</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A198" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A199" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A200" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A201" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A202" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A203" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A204" s="1">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A205" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A206" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A207" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A208" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A209" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A210" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A211" s="1">
-        <v>46052</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A212" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A213" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A214" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A215" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A216" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A217" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A218" s="1">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A219" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A220" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A221" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A222" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A223" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A224" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A225" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A226" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A227" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A228" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A229" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A230" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A231" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A232" s="1">
-        <v>46055</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A233" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A234" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A235" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A236" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A237" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A238" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A239" s="1">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A240" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A241" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A242" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A243" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A244" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A245" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A246" s="1">
-        <v>46057</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A247" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A248" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A249" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A250" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A251" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A252" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A253" s="1">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A254" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A255" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A256" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A257" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A258" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A259" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A260" s="1">
-        <v>46059</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A261" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A262" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A263" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A264" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A265" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A266" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A267" s="1">
-        <v>46060</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A268" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A269" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A270" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A271" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A272" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A273" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A274" s="1">
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A275" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A276" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A277" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A278" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A279" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A280" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A281" s="1">
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A282" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A283" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A284" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A285" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A286" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A287" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A288" s="1">
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A289" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A290" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A291" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A292" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A293" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A294" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A295" s="1">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A296" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A297" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A298" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A299" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A300" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A301" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A302" s="1">
-        <v>46065</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A303" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A304" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A305" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A306" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A307" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A308" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A309" s="1">
-        <v>46066</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A310" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A311" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A312" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A313" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A314" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A315" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A316" s="1">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A317" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A318" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A319" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A320" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A321" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A322" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A323" s="1">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A324" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A325" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A326" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A327" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A328" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A329" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A330" s="1">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A331" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A332" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A333" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A334" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A335" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A336" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A337" s="1">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A338" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A339" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A340" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A341" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A342" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A343" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A344" s="1">
-        <v>46071</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A345" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A346" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A347" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A348" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A349" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A350" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A351" s="1">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A352" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A353" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A354" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A355" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A356" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A357" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A358" s="1">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A359" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A360" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A361" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A362" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A363" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A364" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A365" s="1">
-        <v>46074</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A366" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A367" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A368" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A369" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A370" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A371" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A372" s="1">
-        <v>46075</v>
-      </c>
-    </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A373" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A374" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A375" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A376" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A377" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A378" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A379" s="1">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A380" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A381" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A382" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A383" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A384" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A385" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A386" s="1">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A387" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A388" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A389" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A390" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A391" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A392" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A393" s="1">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A394" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A395" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A396" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A397" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A398" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A399" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A400" s="1">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A401" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A402" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A403" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A404" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A405" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A406" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A407" s="1">
-        <v>46080</v>
-      </c>
-    </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A408" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A409" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A410" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A411" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A412" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A413" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A414" s="1">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A415" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A416" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A417" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A418" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A419" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A420" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A421" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A422" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A423" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A424" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A425" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A426" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A427" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A428" s="1">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A429" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A430" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A431" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A432" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A433" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A434" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A435" s="1">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A436" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A437" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A438" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A439" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A440" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A441" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A442" s="1">
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A443" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A444" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A445" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A446" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A447" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A448" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A449" s="1">
-        <v>46086</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A450" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A451" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A452" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A453" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A454" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A455" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A456" s="1">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A457" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A458" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A459" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A460" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A461" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A462" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A463" s="1">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A464" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A465" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A466" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A467" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A468" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A469" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A470" s="1">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A471" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A472" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A473" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A474" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A475" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A476" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A477" s="1">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A478" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A479" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A480" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A481" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A482" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A483" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A484" s="1">
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A485" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A486" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A487" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A488" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A489" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A490" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A491" s="1">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A492" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A493" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A494" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A495" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A496" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A497" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A498" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A499" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A500" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A501" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A502" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A503" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A504" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A505" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A506" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A507" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A508" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A509" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A510" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A511" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A512" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A513" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A514" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A515" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A516" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A517" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A518" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A519" s="1">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A520" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A521" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A522" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A523" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A524" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A525" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A526" s="1">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A527" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A528" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A529" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A530" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="531" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A531" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="532" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A532" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A533" s="1">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A534" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A535" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A536" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A537" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A538" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A539" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A540" s="1">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="541" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A541" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="542" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A542" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="543" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A543" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="544" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A544" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="545" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A545" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="546" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A546" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="547" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A547" s="1">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A548" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A549" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A550" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="551" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A551" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="552" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A552" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="553" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A553" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="554" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A554" s="1">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="555" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A555" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="556" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A556" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="557" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A557" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="558" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A558" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="559" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A559" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="560" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A560" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="561" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A561" s="1">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="562" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A562" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A563" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="564" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A564" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A565" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A566" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A567" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A568" s="1">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A569" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="570" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A570" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A571" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="572" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A572" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="573" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A573" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="574" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A574" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="575" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A575" s="1">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="576" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A576" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="577" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A577" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="578" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A578" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="579" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A579" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="580" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A580" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="581" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A581" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="582" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A582" s="1">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="583" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A583" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="584" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A584" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="585" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A585" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="586" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A586" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="587" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A587" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="588" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A588" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="589" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A589" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="590" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A590" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="591" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A591" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="592" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A592" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="593" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A593" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="594" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A594" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="595" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A595" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="596" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A596" s="1">
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="597" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A597" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A598" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="599" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A599" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="600" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A600" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="601" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A601" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="602" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A602" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="603" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A603" s="1">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="604" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A604" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="605" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A605" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="606" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A606" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="607" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A607" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="608" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A608" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="609" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A609" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="610" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A610" s="1">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="611" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A611" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="612" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A612" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="613" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A613" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="614" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A614" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="615" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A615" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="616" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A616" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="617" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A617" s="1">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="618" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A618" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="619" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A619" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="620" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A620" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="621" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A621" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="622" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A622" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="623" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A623" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="624" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A624" s="1">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="625" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A625" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="626" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A626" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="627" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A627" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="628" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A628" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="629" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A629" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="630" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A630" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="631" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A631" s="1">
-        <v>46112</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:A631" xr:uid="{810DBB15-66F7-4FDC-B41A-E2B67BC77525}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9DF9A6-0C08-403F-A9B1-CAF23A93F41D}">
-  <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>46030</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>46031</v>
-      </c>
-      <c r="C3" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>46032</v>
-      </c>
-      <c r="C4" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>46033</v>
-      </c>
-      <c r="C5" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>46034</v>
-      </c>
-      <c r="C6" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>46035</v>
-      </c>
-      <c r="C7" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>46036</v>
-      </c>
-      <c r="C8" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>46037</v>
-      </c>
-      <c r="C9" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>46038</v>
-      </c>
-      <c r="C10" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>46039</v>
-      </c>
-      <c r="C11" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>46040</v>
-      </c>
-      <c r="C12" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>46041</v>
-      </c>
-      <c r="C13" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>46042</v>
-      </c>
-      <c r="C14" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>46043</v>
-      </c>
-      <c r="C15" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>46044</v>
-      </c>
-      <c r="C16" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>46045</v>
-      </c>
-      <c r="C17" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>46046</v>
-      </c>
-      <c r="C18" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>46047</v>
-      </c>
-      <c r="C19" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>46048</v>
-      </c>
-      <c r="C20" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>46049</v>
-      </c>
-      <c r="C21" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>46050</v>
-      </c>
-      <c r="C22" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>46051</v>
-      </c>
-      <c r="C23" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>46052</v>
-      </c>
-      <c r="C24" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>46053</v>
-      </c>
-      <c r="C25" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>46054</v>
-      </c>
-      <c r="C26" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>46055</v>
-      </c>
-      <c r="C27" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>46056</v>
-      </c>
-      <c r="C28" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>46057</v>
-      </c>
-      <c r="C29" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>46058</v>
-      </c>
-      <c r="C30" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>46059</v>
-      </c>
-      <c r="C31" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
-        <v>46060</v>
-      </c>
-      <c r="C32" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
-        <v>46061</v>
-      </c>
-      <c r="C33" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>46062</v>
-      </c>
-      <c r="C34" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>46063</v>
-      </c>
-      <c r="C35" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>46064</v>
-      </c>
-      <c r="C36" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
-        <v>46065</v>
-      </c>
-      <c r="C37" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
-        <v>46066</v>
-      </c>
-      <c r="C38" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>46067</v>
-      </c>
-      <c r="C39" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
-        <v>46068</v>
-      </c>
-      <c r="C40" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
-        <v>46069</v>
-      </c>
-      <c r="C41" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>46070</v>
-      </c>
-      <c r="C42" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>46071</v>
-      </c>
-      <c r="C43" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>46072</v>
-      </c>
-      <c r="C44" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>46073</v>
-      </c>
-      <c r="C45" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>46074</v>
-      </c>
-      <c r="C46" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>46075</v>
-      </c>
-      <c r="C47" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>46076</v>
-      </c>
-      <c r="C48" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>46077</v>
-      </c>
-      <c r="C49" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>46078</v>
-      </c>
-      <c r="C50" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>46079</v>
-      </c>
-      <c r="C51" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>46080</v>
-      </c>
-      <c r="C52" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>46081</v>
-      </c>
-      <c r="C53" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>46082</v>
-      </c>
-      <c r="C54" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>46083</v>
-      </c>
-      <c r="C55" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>46084</v>
-      </c>
-      <c r="C56" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>46085</v>
-      </c>
-      <c r="C57" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>46086</v>
-      </c>
-      <c r="C58" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>46087</v>
-      </c>
-      <c r="C59" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>46088</v>
-      </c>
-      <c r="C60" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
-        <v>46089</v>
-      </c>
-      <c r="C61" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
-        <v>46090</v>
-      </c>
-      <c r="C62" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
-        <v>46091</v>
-      </c>
-      <c r="C63" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
-        <v>46092</v>
-      </c>
-      <c r="C64" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
-        <v>46093</v>
-      </c>
-      <c r="C65" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
-        <v>46094</v>
-      </c>
-      <c r="C66" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
-        <v>46095</v>
-      </c>
-      <c r="C67" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
-        <v>46096</v>
-      </c>
-      <c r="C68" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
